--- a/User study data/analysis-ready dataset.xlsx
+++ b/User study data/analysis-ready dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dd\Desktop\INFO 5356 HRI\info5356-lab-2\User study data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7C8E01-C3DC-4354-A10A-90275A2A327E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4F792F-37C5-429F-BE69-F2E1C541F1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9765" windowHeight="11520" xr2:uid="{5952F576-61D0-4DBA-9C4D-B46EABBCE220}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" xr2:uid="{5952F576-61D0-4DBA-9C4D-B46EABBCE220}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>Participant_id</t>
   </si>
@@ -186,6 +186,27 @@
   </si>
   <si>
     <t>The feedback is cute and instant. P04 thinks it is glad to interact with. When the answer is correct, Reachy Mini showed physical movements to mimic human movements and it is interesting.</t>
+  </si>
+  <si>
+    <t>protocol deviation</t>
+  </si>
+  <si>
+    <t>repeated questions</t>
+  </si>
+  <si>
+    <t>repeated questions+ failed interaction</t>
+  </si>
+  <si>
+    <t>Repeated question</t>
+  </si>
+  <si>
+    <t>Interrupted process</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Repeated questions + Failed interaction + Interrupted process</t>
   </si>
 </sst>
 </file>
@@ -569,25 +590,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D91D18C-55A3-4E47-87D3-4B1FB1EB770F}">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="10.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="11.625" customWidth="1"/>
-    <col min="16" max="16" width="12.25" customWidth="1"/>
-    <col min="18" max="18" width="12.75" customWidth="1"/>
-    <col min="19" max="19" width="12.375" customWidth="1"/>
-    <col min="20" max="20" width="11.75" customWidth="1"/>
-    <col min="22" max="22" width="12.375" customWidth="1"/>
-    <col min="24" max="24" width="19.25" customWidth="1"/>
-    <col min="25" max="25" width="33.375" customWidth="1"/>
-    <col min="26" max="26" width="21.125" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="164.625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="63.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -666,8 +699,11 @@
       <c r="Z1" t="s">
         <v>39</v>
       </c>
+      <c r="AA1" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -746,8 +782,11 @@
       <c r="Z2" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="AA2" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -826,8 +865,11 @@
       <c r="Z3" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="AA3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -906,8 +948,11 @@
       <c r="Z4" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="AA4" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -986,8 +1031,11 @@
       <c r="Z5" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="AA5" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1066,8 +1114,11 @@
       <c r="Z6" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="AA6" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1146,8 +1197,11 @@
       <c r="Z7" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="AA7" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1226,8 +1280,11 @@
       <c r="Z8" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AA8" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="9" spans="1:26" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1305,6 +1362,9 @@
       </c>
       <c r="Z9" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/User study data/analysis-ready dataset.xlsx
+++ b/User study data/analysis-ready dataset.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dd\Desktop\INFO 5356 HRI\info5356-lab-2\User study data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4F792F-37C5-429F-BE69-F2E1C541F1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D0CDEA-04D7-4DD6-A369-6056AA0725A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" xr2:uid="{5952F576-61D0-4DBA-9C4D-B46EABBCE220}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" activeTab="1" xr2:uid="{5952F576-61D0-4DBA-9C4D-B46EABBCE220}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="analysis-ready dataset" sheetId="1" r:id="rId1"/>
+    <sheet name="data dictionary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="118">
   <si>
     <t>Participant_id</t>
   </si>
@@ -207,13 +208,199 @@
   </si>
   <si>
     <t>Repeated questions + Failed interaction + Interrupted process</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Type / Scale</t>
+  </si>
+  <si>
+    <t>Missing-data code</t>
+  </si>
+  <si>
+    <t>participant_id</t>
+  </si>
+  <si>
+    <t>De-identified participant identifier</t>
+  </si>
+  <si>
+    <t>P01–P04</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Experimental condition</t>
+  </si>
+  <si>
+    <t>A / B</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>Order of conditions experienced</t>
+  </si>
+  <si>
+    <t>AB / BA</t>
+  </si>
+  <si>
+    <t>warm</t>
+  </si>
+  <si>
+    <t>HRIES Warm item</t>
+  </si>
+  <si>
+    <t>1–7 Likert</t>
+  </si>
+  <si>
+    <t>likeable</t>
+  </si>
+  <si>
+    <t>HRIES Likeable item</t>
+  </si>
+  <si>
+    <t>trustworthy</t>
+  </si>
+  <si>
+    <t>HRIES Trustworthy item</t>
+  </si>
+  <si>
+    <t>friendly</t>
+  </si>
+  <si>
+    <t>HRIES Friendly item</t>
+  </si>
+  <si>
+    <t>alive</t>
+  </si>
+  <si>
+    <t>HRIES Alive item</t>
+  </si>
+  <si>
+    <t>natural</t>
+  </si>
+  <si>
+    <t>HRIES Natural item</t>
+  </si>
+  <si>
+    <t>real</t>
+  </si>
+  <si>
+    <t>HRIES Real item</t>
+  </si>
+  <si>
+    <t>human_like</t>
+  </si>
+  <si>
+    <t>HRIES Human-like item</t>
+  </si>
+  <si>
+    <t>creepy</t>
+  </si>
+  <si>
+    <t>HRIES Creepy item</t>
+  </si>
+  <si>
+    <t>scary</t>
+  </si>
+  <si>
+    <t>HRIES Scary item</t>
+  </si>
+  <si>
+    <t>uncanny</t>
+  </si>
+  <si>
+    <t>HRIES Uncanny item</t>
+  </si>
+  <si>
+    <t>weird</t>
+  </si>
+  <si>
+    <t>HRIES Weird item</t>
+  </si>
+  <si>
+    <t>self_reliant</t>
+  </si>
+  <si>
+    <t>HRIES Self-reliant item</t>
+  </si>
+  <si>
+    <t>rational</t>
+  </si>
+  <si>
+    <t>HRIES Rational item</t>
+  </si>
+  <si>
+    <t>intentional</t>
+  </si>
+  <si>
+    <t>HRIES Intentional item</t>
+  </si>
+  <si>
+    <t>intelligent</t>
+  </si>
+  <si>
+    <t>HRIES Intelligent item</t>
+  </si>
+  <si>
+    <t>Mean of 4 Sociability items</t>
+  </si>
+  <si>
+    <t>1–7</t>
+  </si>
+  <si>
+    <t>Mean of 4 Animacy items</t>
+  </si>
+  <si>
+    <t>Mean of 4 Disturbance items</t>
+  </si>
+  <si>
+    <t>Mean of 4 Agency items</t>
+  </si>
+  <si>
+    <t>manipulation_check</t>
+  </si>
+  <si>
+    <t>Perceived intended behavioral difference</t>
+  </si>
+  <si>
+    <t>objective_measure</t>
+  </si>
+  <si>
+    <t>Performance measure from the task</t>
+  </si>
+  <si>
+    <t>qualitative_response</t>
+  </si>
+  <si>
+    <t>Participant's open-ended response</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>protocol_deviation</t>
+  </si>
+  <si>
+    <t>Any deviation from planned protocol</t>
+  </si>
+  <si>
+    <t>1–5 Likert</t>
+  </si>
+  <si>
+    <t>Time duration in minutes and seconds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +414,20 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -249,12 +450,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,7 +801,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D91D18C-55A3-4E47-87D3-4B1FB1EB770F}">
   <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
@@ -620,7 +830,7 @@
     <col min="27" max="27" width="63.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -703,7 +913,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:27" ht="14.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -786,7 +996,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:27" ht="14.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -869,7 +1079,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:27" ht="14.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -952,7 +1162,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:27" ht="14.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1035,7 +1245,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:27" ht="14.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1118,7 +1328,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:27" ht="14.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1201,7 +1411,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:27" ht="14.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1284,7 +1494,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:27" ht="14.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1365,6 +1575,414 @@
       </c>
       <c r="AA9" t="s">
         <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16635525-19E0-4A10-8A5A-2E3D977020AE}">
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="40.5">
+      <c r="A1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="94.5">
+      <c r="A2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="54">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="67.5">
+      <c r="A4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="40.5">
+      <c r="A5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="40.5">
+      <c r="A6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="40.5">
+      <c r="A7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="40.5">
+      <c r="A8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="40.5">
+      <c r="A9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="40.5">
+      <c r="A10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="40.5">
+      <c r="A11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="54">
+      <c r="A12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="40.5">
+      <c r="A13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="40.5">
+      <c r="A14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="40.5">
+      <c r="A15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="40.5">
+      <c r="A16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="54">
+      <c r="A17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="40.5">
+      <c r="A18" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="40.5">
+      <c r="A19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="40.5">
+      <c r="A20" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="67.5">
+      <c r="A21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="54">
+      <c r="A22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="67.5">
+      <c r="A23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="40.5">
+      <c r="A24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="54">
+      <c r="A25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="54">
+      <c r="A26" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="67.5">
+      <c r="A27" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="54">
+      <c r="A28" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
